--- a/Datos/Alumnos.xlsx
+++ b/Datos/Alumnos.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FAVIO\Documents\TECBA 2025\DESING LAB 2025\PRAGRAMACION I\APP\datos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MI CARPETA\TECBA\PROGRAMACIÓN\DESIGNLAB\Designlab_Programaci-n\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8E09C5B-FB97-4FD9-A319-E1FA3ADC493A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="16200" windowHeight="9360" xr2:uid="{633A2E90-4719-4275-853A-000D683A436E}"/>
+    <workbookView xWindow="2736" yWindow="2736" windowWidth="16200" windowHeight="9360"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,47 +38,47 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
-    <t>Mat</t>
-  </si>
-  <si>
-    <t>Fis</t>
-  </si>
-  <si>
-    <t>Qui</t>
-  </si>
-  <si>
-    <t>Nombre del Alumno</t>
-  </si>
-  <si>
-    <t>favio alvarez</t>
-  </si>
-  <si>
-    <t>jose carlos vasquez</t>
-  </si>
-  <si>
-    <t>armando diaz</t>
-  </si>
-  <si>
-    <t>luis vargas</t>
-  </si>
-  <si>
-    <t>fernanda flores</t>
-  </si>
-  <si>
-    <t>victor antelo</t>
-  </si>
-  <si>
-    <t>juan soliz</t>
-  </si>
-  <si>
-    <t>ana salas</t>
+    <t>Matemáticas</t>
+  </si>
+  <si>
+    <t>Física</t>
+  </si>
+  <si>
+    <t>Química</t>
+  </si>
+  <si>
+    <t>Estudiante</t>
+  </si>
+  <si>
+    <t>Favio Alvarez</t>
+  </si>
+  <si>
+    <t>Jose Carlos Vasquez</t>
+  </si>
+  <si>
+    <t>Armando Diaz</t>
+  </si>
+  <si>
+    <t>Luis Vargas</t>
+  </si>
+  <si>
+    <t>Fernanda Flores</t>
+  </si>
+  <si>
+    <t>Victor Antelo</t>
+  </si>
+  <si>
+    <t>Juan Soliz</t>
+  </si>
+  <si>
+    <t>Ana Salas</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -87,16 +86,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -104,12 +117,222 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -423,140 +646,141 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0B30112-98E5-4405-ADA4-05FF67CBB16A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.28515625" customWidth="1"/>
+    <col min="1" max="1" width="20.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="12" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="8">
         <v>10</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="8">
         <v>9</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="9">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="1">
         <v>10</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>9</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="3">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="1">
         <v>9</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>8</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="1">
         <v>8</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>6</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="3">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="1">
         <v>6</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="1">
         <v>5</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="3">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="1">
         <v>7</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="1">
         <v>7</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="3">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="1">
         <v>8</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="1">
         <v>9</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="3">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="5">
         <v>10</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="5">
         <v>8</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="6">
         <v>8</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>